--- a/artfynd/A 5414-2025 artfynd.xlsx
+++ b/artfynd/A 5414-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1484,6 +1484,120 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123132774</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57484</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 5414, Gamlebyn, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>589120</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6447182</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Valdemarsvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tryserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Ulf Hjulström, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5414-2025 artfynd.xlsx
+++ b/artfynd/A 5414-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123087386</v>
+        <v>123086764</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
+        <v>91312</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -726,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588835</v>
+        <v>589025</v>
       </c>
       <c r="R2" t="n">
-        <v>6447244</v>
+        <v>6447273</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>gammal grov tall</t>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,17 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123093960</v>
+        <v>123086411</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>94982</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,49 +802,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588913</v>
+        <v>589064</v>
       </c>
       <c r="R3" t="n">
-        <v>6447206</v>
+        <v>6447371</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,34 +880,40 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på och runt en barrträdsstubbe</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123086764</v>
+        <v>123087386</v>
       </c>
       <c r="B4" t="n">
-        <v>91304</v>
+        <v>90972</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,28 +922,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1506</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -951,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589025</v>
+        <v>588835</v>
       </c>
       <c r="R4" t="n">
-        <v>6447273</v>
+        <v>6447244</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +1001,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>asplåga</t>
+          <t>gammal grov tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,17 +1022,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123086992</v>
+        <v>123093960</v>
       </c>
       <c r="B5" t="n">
-        <v>90964</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,48 +1045,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588968</v>
+        <v>588913</v>
       </c>
       <c r="R5" t="n">
-        <v>6447135</v>
+        <v>6447206</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,40 +1115,34 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>grov gammal tall</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123093996</v>
+        <v>123093992</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,37 +1151,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1252,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123086411</v>
+        <v>123086992</v>
       </c>
       <c r="B7" t="n">
-        <v>94974</v>
+        <v>90972</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,39 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589064</v>
+        <v>588968</v>
       </c>
       <c r="R7" t="n">
-        <v>6447371</v>
+        <v>6447135</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på och runt en barrträdsstubbe</t>
+          <t>grov gammal tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123093992</v>
+        <v>123093996</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,37 +1384,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 5414-2025 artfynd.xlsx
+++ b/artfynd/A 5414-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123086764</v>
+        <v>123093992</v>
       </c>
       <c r="B2" t="n">
-        <v>91312</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1506</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589025</v>
+        <v>589129</v>
       </c>
       <c r="R2" t="n">
-        <v>6447273</v>
+        <v>6447245</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,30 +765,24 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>asplåga</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1029,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123093960</v>
+        <v>123086764</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>91312</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,49 +1040,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588913</v>
+        <v>589025</v>
       </c>
       <c r="R5" t="n">
-        <v>6447206</v>
+        <v>6447273</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,34 +1113,40 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>asplåga</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123093992</v>
+        <v>123093960</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,33 +1159,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589129</v>
+        <v>588913</v>
       </c>
       <c r="R6" t="n">
-        <v>6447245</v>
+        <v>6447206</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 5414-2025 artfynd.xlsx
+++ b/artfynd/A 5414-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123093992</v>
+        <v>123093960</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589129</v>
+        <v>588913</v>
       </c>
       <c r="R2" t="n">
-        <v>6447245</v>
+        <v>6447206</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123086411</v>
+        <v>123087386</v>
       </c>
       <c r="B3" t="n">
-        <v>94982</v>
+        <v>90972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +797,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589064</v>
+        <v>588835</v>
       </c>
       <c r="R3" t="n">
-        <v>6447371</v>
+        <v>6447244</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på och runt en barrträdsstubbe</t>
+          <t>gammal grov tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,14 +897,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123087386</v>
+        <v>123086992</v>
       </c>
       <c r="B4" t="n">
         <v>90972</v>
@@ -944,7 +939,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -960,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588835</v>
+        <v>588968</v>
       </c>
       <c r="R4" t="n">
-        <v>6447244</v>
+        <v>6447135</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,7 +995,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>gammal grov tall</t>
+          <t>grov gammal tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,17 +1016,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123086764</v>
+        <v>123093996</v>
       </c>
       <c r="B5" t="n">
-        <v>91312</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,48 +1035,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1506</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589025</v>
+        <v>589129</v>
       </c>
       <c r="R5" t="n">
-        <v>6447273</v>
+        <v>6447245</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,40 +1113,34 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>asplåga</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123093960</v>
+        <v>123086411</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>94982</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,49 +1149,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588913</v>
+        <v>589064</v>
       </c>
       <c r="R6" t="n">
-        <v>6447206</v>
+        <v>6447371</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,34 +1227,40 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på och runt en barrträdsstubbe</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123086992</v>
+        <v>123086764</v>
       </c>
       <c r="B7" t="n">
-        <v>90972</v>
+        <v>91312</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,32 +1269,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>1506</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588968</v>
+        <v>589025</v>
       </c>
       <c r="R7" t="n">
-        <v>6447135</v>
+        <v>6447273</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>grov gammal tall</t>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123093996</v>
+        <v>123093992</v>
       </c>
       <c r="B8" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,37 +1384,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 5414-2025 artfynd.xlsx
+++ b/artfynd/A 5414-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123093960</v>
+        <v>123093992</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588913</v>
+        <v>589129</v>
       </c>
       <c r="R2" t="n">
-        <v>6447206</v>
+        <v>6447245</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123087386</v>
+        <v>123086992</v>
       </c>
       <c r="B3" t="n">
         <v>90972</v>
@@ -820,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588835</v>
+        <v>588968</v>
       </c>
       <c r="R3" t="n">
-        <v>6447244</v>
+        <v>6447135</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +880,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>gammal grov tall</t>
+          <t>grov gammal tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,14 +901,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123086992</v>
+        <v>123087386</v>
       </c>
       <c r="B4" t="n">
         <v>90972</v>
@@ -939,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -955,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588968</v>
+        <v>588835</v>
       </c>
       <c r="R4" t="n">
-        <v>6447135</v>
+        <v>6447244</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>grov gammal tall</t>
+          <t>gammal grov tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,17 +1020,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123093996</v>
+        <v>123093960</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,20 +1039,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,16 +1060,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589129</v>
+        <v>588913</v>
       </c>
       <c r="R5" t="n">
-        <v>6447245</v>
+        <v>6447206</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123086411</v>
+        <v>123093996</v>
       </c>
       <c r="B6" t="n">
-        <v>94982</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,49 +1153,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589064</v>
+        <v>589129</v>
       </c>
       <c r="R6" t="n">
-        <v>6447371</v>
+        <v>6447245</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,30 +1227,24 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på och runt en barrträdsstubbe</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1372,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123093992</v>
+        <v>123086411</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>94982</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,53 +1378,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589129</v>
+        <v>589064</v>
       </c>
       <c r="R8" t="n">
-        <v>6447245</v>
+        <v>6447371</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,24 +1456,30 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på och runt en barrträdsstubbe</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 5414-2025 artfynd.xlsx
+++ b/artfynd/A 5414-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123093992</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123086992</v>
+        <v>123086411</v>
       </c>
       <c r="B3" t="n">
-        <v>90972</v>
+        <v>94985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +801,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588968</v>
+        <v>589064</v>
       </c>
       <c r="R3" t="n">
-        <v>6447135</v>
+        <v>6447371</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +881,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>grov gammal tall</t>
+          <t>på och runt en barrträdsstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +912,7 @@
         <v>123087386</v>
       </c>
       <c r="B4" t="n">
-        <v>90972</v>
+        <v>90975</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1030,7 +1031,7 @@
         <v>123093960</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1137,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123093996</v>
+        <v>123086992</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
+        <v>90975</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,25 +1150,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,27 +1176,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589129</v>
+        <v>588968</v>
       </c>
       <c r="R6" t="n">
-        <v>6447245</v>
+        <v>6447135</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,24 +1227,30 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>grov gammal tall</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1254,7 +1260,7 @@
         <v>123086764</v>
       </c>
       <c r="B7" t="n">
-        <v>91312</v>
+        <v>91315</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1366,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123086411</v>
+        <v>123093996</v>
       </c>
       <c r="B8" t="n">
-        <v>94982</v>
+        <v>57851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,49 +1388,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589064</v>
+        <v>589129</v>
       </c>
       <c r="R8" t="n">
-        <v>6447371</v>
+        <v>6447245</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,30 +1462,24 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på och runt en barrträdsstubbe</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
         <v>123132774</v>
       </c>
       <c r="B9" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 5414-2025 artfynd.xlsx
+++ b/artfynd/A 5414-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123093992</v>
+        <v>123093996</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>57851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123086411</v>
+        <v>123093960</v>
       </c>
       <c r="B3" t="n">
-        <v>94985</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,53 +801,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589064</v>
+        <v>588913</v>
       </c>
       <c r="R3" t="n">
-        <v>6447371</v>
+        <v>6447206</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,40 +875,34 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på och runt en barrträdsstubbe</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123087386</v>
+        <v>123086764</v>
       </c>
       <c r="B4" t="n">
-        <v>90975</v>
+        <v>91317</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,32 +911,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -960,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588835</v>
+        <v>589025</v>
       </c>
       <c r="R4" t="n">
-        <v>6447244</v>
+        <v>6447273</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,7 +986,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>gammal grov tall</t>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,17 +1007,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123093960</v>
+        <v>123086411</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>94987</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,49 +1026,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588913</v>
+        <v>589064</v>
       </c>
       <c r="R5" t="n">
-        <v>6447206</v>
+        <v>6447371</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,24 +1104,30 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på och runt en barrträdsstubbe</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1141,7 +1137,7 @@
         <v>123086992</v>
       </c>
       <c r="B6" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1257,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123086764</v>
+        <v>123087386</v>
       </c>
       <c r="B7" t="n">
-        <v>91315</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,28 +1265,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1506</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589025</v>
+        <v>588835</v>
       </c>
       <c r="R7" t="n">
-        <v>6447273</v>
+        <v>6447244</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>asplåga</t>
+          <t>gammal grov tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,17 +1365,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123093996</v>
+        <v>123093992</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>57634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,37 +1384,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>

--- a/artfynd/A 5414-2025 artfynd.xlsx
+++ b/artfynd/A 5414-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123093996</v>
+        <v>123093992</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123093960</v>
+        <v>123087386</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,45 +805,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588913</v>
+        <v>588835</v>
       </c>
       <c r="R3" t="n">
-        <v>6447206</v>
+        <v>6447244</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,24 +878,30 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>gammal grov tall</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -902,7 +911,7 @@
         <v>123086764</v>
       </c>
       <c r="B4" t="n">
-        <v>91317</v>
+        <v>91323</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1017,7 +1026,7 @@
         <v>123086411</v>
       </c>
       <c r="B5" t="n">
-        <v>94987</v>
+        <v>94993</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1134,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123086992</v>
+        <v>123093960</v>
       </c>
       <c r="B6" t="n">
-        <v>90977</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,48 +1159,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588968</v>
+        <v>588913</v>
       </c>
       <c r="R6" t="n">
-        <v>6447135</v>
+        <v>6447206</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,40 +1229,34 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>grov gammal tall</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123087386</v>
+        <v>123093996</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>57851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,49 +1265,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588835</v>
+        <v>589129</v>
       </c>
       <c r="R7" t="n">
-        <v>6447244</v>
+        <v>6447245</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1342,40 +1343,34 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>gammal grov tall</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123093992</v>
+        <v>123086992</v>
       </c>
       <c r="B8" t="n">
-        <v>57634</v>
+        <v>90983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,49 +1383,48 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589129</v>
+        <v>588968</v>
       </c>
       <c r="R8" t="n">
-        <v>6447245</v>
+        <v>6447135</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,24 +1456,30 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>grov gammal tall</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 5414-2025 artfynd.xlsx
+++ b/artfynd/A 5414-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123086992</v>
+        <v>123093992</v>
       </c>
       <c r="B2" t="n">
-        <v>90986</v>
+        <v>57640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,48 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588968</v>
+        <v>589129</v>
       </c>
       <c r="R2" t="n">
-        <v>6447135</v>
+        <v>6447245</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,40 +765,34 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>grov gammal tall</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123093960</v>
+        <v>123086411</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>95013</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,49 +801,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588913</v>
+        <v>589064</v>
       </c>
       <c r="R3" t="n">
-        <v>6447206</v>
+        <v>6447371</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,24 +879,30 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på och runt en barrträdsstubbe</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -907,7 +912,7 @@
         <v>123087386</v>
       </c>
       <c r="B4" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123086764</v>
+        <v>123086992</v>
       </c>
       <c r="B5" t="n">
-        <v>91326</v>
+        <v>91003</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,28 +1040,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1506</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1070,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589025</v>
+        <v>588968</v>
       </c>
       <c r="R5" t="n">
-        <v>6447273</v>
+        <v>6447135</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,7 +1119,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>asplåga</t>
+          <t>grov gammal tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123093996</v>
+        <v>123086764</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>91343</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,53 +1159,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>1506</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589129</v>
+        <v>589025</v>
       </c>
       <c r="R6" t="n">
-        <v>6447245</v>
+        <v>6447273</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,34 +1232,40 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>asplåga</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123093992</v>
+        <v>123093960</v>
       </c>
       <c r="B7" t="n">
-        <v>57634</v>
+        <v>57503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,33 +1278,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1304,13 +1310,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589129</v>
+        <v>588913</v>
       </c>
       <c r="R7" t="n">
-        <v>6447245</v>
+        <v>6447206</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123086411</v>
+        <v>123093996</v>
       </c>
       <c r="B8" t="n">
-        <v>94996</v>
+        <v>57857</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,49 +1388,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589064</v>
+        <v>589129</v>
       </c>
       <c r="R8" t="n">
-        <v>6447371</v>
+        <v>6447245</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,30 +1462,24 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på och runt en barrträdsstubbe</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
         <v>123132774</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 5414-2025 artfynd.xlsx
+++ b/artfynd/A 5414-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123093992</v>
+        <v>123086764</v>
       </c>
       <c r="B2" t="n">
-        <v>57640</v>
+        <v>91348</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589129</v>
+        <v>589025</v>
       </c>
       <c r="R2" t="n">
-        <v>6447245</v>
+        <v>6447273</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,34 +760,40 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>asplåga</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123086411</v>
+        <v>123093996</v>
       </c>
       <c r="B3" t="n">
-        <v>95013</v>
+        <v>57860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,49 +806,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589064</v>
+        <v>589129</v>
       </c>
       <c r="R3" t="n">
-        <v>6447371</v>
+        <v>6447245</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,40 +880,34 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på och runt en barrträdsstubbe</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123087386</v>
+        <v>123093992</v>
       </c>
       <c r="B4" t="n">
-        <v>91003</v>
+        <v>57643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,45 +920,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588835</v>
+        <v>589129</v>
       </c>
       <c r="R4" t="n">
-        <v>6447244</v>
+        <v>6447245</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,30 +994,24 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>gammal grov tall</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1031,7 +1021,7 @@
         <v>123086992</v>
       </c>
       <c r="B5" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1147,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123086764</v>
+        <v>123086411</v>
       </c>
       <c r="B6" t="n">
-        <v>91343</v>
+        <v>95019</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1149,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1506</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1194,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589025</v>
+        <v>589064</v>
       </c>
       <c r="R6" t="n">
-        <v>6447273</v>
+        <v>6447371</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,7 +1229,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>asplåga</t>
+          <t>på och runt en barrträdsstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,7 +1260,7 @@
         <v>123093960</v>
       </c>
       <c r="B7" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1372,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123093996</v>
+        <v>123087386</v>
       </c>
       <c r="B8" t="n">
-        <v>57857</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,50 +1379,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589129</v>
+        <v>588835</v>
       </c>
       <c r="R8" t="n">
-        <v>6447245</v>
+        <v>6447244</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1462,24 +1456,30 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>gammal grov tall</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
         <v>123132774</v>
       </c>
       <c r="B9" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Ulf Hjulström, Jan Aronsson</t>
+          <t>Jan Aronsson, Ulf Hjulström, Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 5414-2025 artfynd.xlsx
+++ b/artfynd/A 5414-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123086764</v>
+        <v>123087386</v>
       </c>
       <c r="B2" t="n">
-        <v>91348</v>
+        <v>91010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1506</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -722,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589025</v>
+        <v>588835</v>
       </c>
       <c r="R2" t="n">
-        <v>6447273</v>
+        <v>6447244</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>asplåga</t>
+          <t>gammal grov tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,17 +787,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123093996</v>
+        <v>123086992</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,27 +832,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589129</v>
+        <v>588968</v>
       </c>
       <c r="R3" t="n">
-        <v>6447245</v>
+        <v>6447135</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,34 +883,40 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>grov gammal tall</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123093992</v>
+        <v>123093996</v>
       </c>
       <c r="B4" t="n">
-        <v>57643</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,37 +925,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1018,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123086992</v>
+        <v>123093992</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,48 +1043,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588968</v>
+        <v>589129</v>
       </c>
       <c r="R5" t="n">
-        <v>6447135</v>
+        <v>6447245</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,40 +1117,34 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>grov gammal tall</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123086411</v>
+        <v>123093960</v>
       </c>
       <c r="B6" t="n">
-        <v>95019</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,53 +1153,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A5414-2025, Sm</t>
+          <t>A 5414, Gamlebyn, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589064</v>
+        <v>588913</v>
       </c>
       <c r="R6" t="n">
-        <v>6447371</v>
+        <v>6447206</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,40 +1227,34 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på och runt en barrträdsstubbe</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123093960</v>
+        <v>123086764</v>
       </c>
       <c r="B7" t="n">
-        <v>57506</v>
+        <v>91350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,49 +1263,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 5414, Gamlebyn, Sm</t>
+          <t>A5414-2025, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588913</v>
+        <v>589025</v>
       </c>
       <c r="R7" t="n">
-        <v>6447206</v>
+        <v>6447273</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1343,34 +1336,40 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>asplåga</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson, Ulf Hjulström</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123087386</v>
+        <v>123086411</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>95021</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,38 +1378,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588835</v>
+        <v>589064</v>
       </c>
       <c r="R8" t="n">
-        <v>6447244</v>
+        <v>6447371</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>gammal grov tall</t>
+          <t>på och runt en barrträdsstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Jan Aronsson</t>
+          <t>Stefan Kasselstrand, Jan Aronsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
         <v>123132774</v>
       </c>
       <c r="B9" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Ulf Hjulström, Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Ulf Hjulström, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
